--- a/FinanceDataMigration/src/main/resources/migration-templates/SCHEME.xlsx
+++ b/FinanceDataMigration/src/main/resources/migration-templates/SCHEME.xlsx
@@ -30,7 +30,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">ULB Name </t>
@@ -48,7 +47,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Scheme Name </t>
@@ -66,7 +64,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Fund </t>
@@ -84,7 +81,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Status </t>
@@ -102,7 +98,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">Start Date </t>
@@ -120,7 +115,6 @@
     <r>
       <rPr>
         <b/>
-        <color indexed="64"/>
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">End Date </t>
@@ -169,23 +163,21 @@
     </font>
     <font>
       <b/>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FFC9211E"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color indexed="64"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -234,22 +226,22 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -28840,16 +28832,8 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
-  <dataValidations count="3" disablePrompts="0">
-    <dataValidation sqref="E4:E100" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$G$2:$G$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="B4:B100" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>'DropDown List'!$A$2:$A$95</formula1>
-    </dataValidation>
-    <dataValidation sqref="D4:D100" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="0">
-      <formula1>Fund!$C$4:$C$1000</formula1>
-    </dataValidation>
+  <dataValidations count="1" disablePrompts="0">
+    <dataValidation sqref="1:1048576" type="none" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1"/>
   </dataValidations>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
